--- a/outputs/03_Peptide_Product_and_Pricing_Audit.xlsx
+++ b/outputs/03_Peptide_Product_and_Pricing_Audit.xlsx
@@ -17756,7 +17756,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>AminoLord recommendation [SR]</t>
+          <t>Reserve Clinic recommendation [SR]</t>
         </is>
       </c>
     </row>
@@ -18042,7 +18042,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Model in 07_AminoLord_Financial_Model.xlsx</t>
+          <t>Model in 07_ReserveClinic_Financial_Model.xlsx</t>
         </is>
       </c>
     </row>
@@ -18091,7 +18091,7 @@
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>AminoLord copy rule [SR]</t>
+          <t>Reserve Clinic copy rule [SR]</t>
         </is>
       </c>
     </row>
